--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RskValRelateImportInfo.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RskValRelateImportInfo.xlsx
@@ -10,7 +10,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
@@ -37,7 +36,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>资产名称</t>
+    <t>组合名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
